--- a/excel_routes/route_CAI_YNB_threats.xlsx
+++ b/excel_routes/route_CAI_YNB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -459,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -523,27 +541,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26-FEB-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-943</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-103</t>
+          <t>Nile Air NP-303</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4586</v>
+        <v>4742</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6423</v>
+        <v>5183</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-1837</v>
+        <v>-441</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -568,27 +586,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26-FEB-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-943</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-180</t>
+          <t>Nile Air NP-403</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5270</v>
+        <v>4742</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6423</v>
+        <v>5183</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-1153</v>
+        <v>-441</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -613,27 +631,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>26-FEB-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-943</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-184</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5270</v>
+        <v>4742</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6423</v>
+        <v>5183</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-1153</v>
+        <v>-441</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -658,27 +676,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>27-FEB-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-987</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-113</t>
+          <t>Nesma Airlines NE-186</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4586</v>
+        <v>4728</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6423</v>
+        <v>5183</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1837</v>
+        <v>-455</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -703,27 +721,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>28-FEB-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-987</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-103</t>
+          <t>Nesma Airlines NE-180</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4586</v>
+        <v>4728</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6423</v>
+        <v>5183</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1837</v>
+        <v>-455</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -748,27 +766,27 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>03-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-987</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-103</t>
+          <t>Nile Air NP-113</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5106</v>
+        <v>4742</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6423</v>
+        <v>5183</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1317</v>
+        <v>-441</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -793,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -803,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-103</t>
+          <t>Nesma Airlines NE-180</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4586</v>
+        <v>4728</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6423</v>
+        <v>7733</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1837</v>
+        <v>-3005</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -824,9 +842,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -838,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -848,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-103</t>
+          <t>Nile Air NP-113</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4586</v>
+        <v>4742</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6423</v>
+        <v>7733</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1837</v>
+        <v>-2991</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -869,9 +887,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -883,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -893,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-184</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5270</v>
+        <v>4742</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6423</v>
+        <v>7733</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1153</v>
+        <v>-2991</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -914,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -928,27 +946,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>12-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-987</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-103</t>
+          <t>Nesma Airlines NE-180</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4586</v>
+        <v>4728</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6423</v>
+        <v>5183</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1837</v>
+        <v>-455</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -973,27 +991,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-987</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-180</t>
+          <t>Nile Air NP-113</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5270</v>
+        <v>4742</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6423</v>
+        <v>5183</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1153</v>
+        <v>-441</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1018,27 +1036,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-987</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-186</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5270</v>
+        <v>4742</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6423</v>
+        <v>5183</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1153</v>
+        <v>-441</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1063,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15-MAR-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1073,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-184</t>
+          <t>Nile Air NP-113</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5270</v>
+        <v>5996</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6423</v>
+        <v>16748</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1153</v>
+        <v>-10752</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1094,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1108,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1118,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-180</t>
+          <t>Nesma Airlines NE-186</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5270</v>
+        <v>7733</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>6423</v>
+        <v>16748</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1153</v>
+        <v>-9015</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1139,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1153,27 +1171,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-931</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-303</t>
+          <t>Nile Air NP-113</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4586</v>
+        <v>5996</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>6423</v>
+        <v>9746</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1837</v>
+        <v>-3750</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1184,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1198,27 +1216,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-931</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-103</t>
+          <t>Nesma Airlines NE-186</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4586</v>
+        <v>7733</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>6423</v>
+        <v>9746</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-1837</v>
+        <v>-2013</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1243,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1257,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5270</v>
+        <v>6851</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6423</v>
+        <v>9208</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-1153</v>
+        <v>-2357</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1288,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1298,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-303</t>
+          <t>Nesma Airlines NE-180</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4586</v>
+        <v>4728</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>6423</v>
+        <v>7319</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-1837</v>
+        <v>-2591</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1333,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1343,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-186</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>5270</v>
+        <v>4742</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>6423</v>
+        <v>7319</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-1153</v>
+        <v>-2577</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1378,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1388,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-103</t>
+          <t>Nesma Airlines NE-182</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4586</v>
+        <v>6134</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>6423</v>
+        <v>8147</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-1837</v>
+        <v>-2013</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1423,27 +1441,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-961</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-180</t>
+          <t>Nesma Airlines NE-182</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5270</v>
+        <v>6134</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>6423</v>
+        <v>7319</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-1153</v>
+        <v>-1185</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1468,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>21-MAR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1478,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-186</t>
+          <t>Nesma Airlines NE-182</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>5270</v>
+        <v>6134</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>6423</v>
+        <v>7733</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1153</v>
+        <v>-1599</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1513,27 +1531,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22-MAR-26</t>
+          <t>03-APR-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-961</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-180</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>5929</v>
+        <v>6575</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>6423</v>
+        <v>7319</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-494</v>
+        <v>-744</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1558,27 +1576,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22-MAR-26</t>
+          <t>25-APR-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-182</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>5929</v>
+        <v>7788</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>6423</v>
+        <v>9208</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-494</v>
+        <v>-1420</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>30</v>
@@ -1595,726 +1613,6 @@
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>23-MAR-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-985</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-186</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>5929</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-494</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>23-MAR-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-985</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-180</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>5929</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-494</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>23-MAR-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-985</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-182</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>5929</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-494</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>24-MAR-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>5106</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-1317</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>24-MAR-26</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-303</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>5600</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>-823</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>24-MAR-26</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-180</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>5929</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>-494</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>25-MAR-26</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-186</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>5929</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>-494</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>25-MAR-26</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-180</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>5929</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>-494</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>25-MAR-26</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-184</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>5929</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>-494</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>25-MAR-26</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-182</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>5929</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>-494</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>25-MAR-26</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-113</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>6183</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>-240</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>26-MAR-26</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-113</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>5106</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>-1317</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>26-MAR-26</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-180</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>5929</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>-494</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>29-MAR-26</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-180</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>5929</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>-494</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>31-MAR-26</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-180</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>5929</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>-494</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>31-MAR-26</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-182</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>5929</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>6423</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>-494</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_YNB_threats.xlsx
+++ b/excel_routes/route_CAI_YNB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,12 +58,6 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -477,7 +468,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -541,27 +532,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>24-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-943</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-303</t>
+          <t>Nesma Airlines NE-180</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4742</v>
+        <v>4797</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5183</v>
+        <v>5541</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-441</v>
+        <v>-744</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,27 +577,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>24-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-943</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-403</t>
+          <t>Nesma Airlines NE-180</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4742</v>
+        <v>4797</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5183</v>
+        <v>5541</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-441</v>
+        <v>-744</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,12 +622,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-943</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -645,13 +636,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4742</v>
+        <v>4826</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5183</v>
+        <v>5541</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-441</v>
+        <v>-715</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,27 +667,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-987</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-186</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4728</v>
+        <v>4826</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5183</v>
+        <v>5541</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-455</v>
+        <v>-715</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -721,27 +712,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>03-APR-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-987</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-180</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4728</v>
+        <v>4826</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5183</v>
+        <v>8108</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-455</v>
+        <v>-3282</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,9 +743,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,27 +757,27 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>03-APR-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SM-987</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-113</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4742</v>
+        <v>4826</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5183</v>
+        <v>8108</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-441</v>
+        <v>-3282</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -797,9 +788,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,27 +802,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>03-APR-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-961</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-180</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4728</v>
+        <v>4826</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7733</v>
+        <v>7687</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-3005</v>
+        <v>-2861</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -856,27 +847,27 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>03-APR-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-961</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-113</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4742</v>
+        <v>4826</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7733</v>
+        <v>7687</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-2991</v>
+        <v>-2861</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -901,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>07-APR-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -915,13 +906,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4742</v>
+        <v>6663</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7733</v>
+        <v>7687</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-2991</v>
+        <v>-1024</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -932,9 +923,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,27 +937,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>07-APR-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SM-987</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-180</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4728</v>
+        <v>6663</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5183</v>
+        <v>7687</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-455</v>
+        <v>-1024</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -991,27 +982,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>17-APR-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-987</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-113</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4742</v>
+        <v>6663</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5183</v>
+        <v>7687</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-441</v>
+        <v>-1024</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1036,12 +1027,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>17-APR-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SM-987</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1050,13 +1041,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4742</v>
+        <v>6663</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>5183</v>
+        <v>7687</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-441</v>
+        <v>-1024</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1081,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1082,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-113</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5996</v>
+        <v>9385</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16748</v>
+        <v>11335</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-10752</v>
+        <v>-1950</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>10</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1127,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-186</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7733</v>
+        <v>9385</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16748</v>
+        <v>11335</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-9015</v>
+        <v>-1950</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>10</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,27 +1162,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SM-931</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-113</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5996</v>
+        <v>7898</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>9746</v>
+        <v>9609</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-3750</v>
+        <v>-1711</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1202,9 +1193,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,27 +1207,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SM-931</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-186</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7733</v>
+        <v>7898</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>9746</v>
+        <v>9609</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-2013</v>
+        <v>-1711</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1261,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>29-MAR-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1262,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-180</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6851</v>
+        <v>7281</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>9208</v>
+        <v>7393</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-2357</v>
+        <v>-112</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1306,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1307,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-180</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4728</v>
+        <v>7281</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7319</v>
+        <v>7393</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-2591</v>
+        <v>-112</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1351,12 +1342,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1365,13 +1356,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4742</v>
+        <v>7281</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>7319</v>
+        <v>9609</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-2577</v>
+        <v>-2328</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1396,27 +1387,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-182</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6134</v>
+        <v>7281</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>8147</v>
+        <v>9609</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-2013</v>
+        <v>-2328</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1441,27 +1432,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-182</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6134</v>
+        <v>7281</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>7319</v>
+        <v>7393</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-1185</v>
+        <v>-112</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1486,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1487,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-182</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6134</v>
+        <v>7281</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>7733</v>
+        <v>7393</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1599</v>
+        <v>-112</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1531,12 +1522,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1545,13 +1536,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>6575</v>
+        <v>7281</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>7319</v>
+        <v>9609</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-744</v>
+        <v>-2328</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1576,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>25-APR-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1590,13 +1581,13 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7788</v>
+        <v>7281</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>9208</v>
+        <v>9609</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-1420</v>
+        <v>-2328</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>30</v>
@@ -1613,6 +1604,456 @@
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>16-JUN-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-441</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>7393</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>16-JUN-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-441</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>7393</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>20-JUN-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-447</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>9609</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-2328</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>20-JUN-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-447</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>9609</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-2328</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>23-JUN-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-441</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>7393</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>23-JUN-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-441</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>7393</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>27-JUN-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-447</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>9609</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-2328</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>27-JUN-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-447</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>9609</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-2328</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>30-JUN-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-441</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>7393</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>30-JUN-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-441</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>7393</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_YNB_threats.xlsx
+++ b/excel_routes/route_CAI_YNB_threats.xlsx
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-180</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4797</v>
+        <v>5593</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5541</v>
+        <v>7946</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-744</v>
+        <v>-2353</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-180</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4797</v>
+        <v>4832</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5541</v>
+        <v>7946</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-744</v>
+        <v>-3114</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -608,9 +608,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -622,12 +622,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -636,13 +636,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4826</v>
+        <v>7298</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5541</v>
+        <v>10708</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-715</v>
+        <v>-3410</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -653,9 +653,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4826</v>
+        <v>9412</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5541</v>
+        <v>10708</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-715</v>
+        <v>-1296</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -712,12 +712,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4826</v>
+        <v>9412</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8108</v>
+        <v>10159</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-3282</v>
+        <v>-747</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -743,9 +743,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4826</v>
+        <v>7918</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8108</v>
+        <v>8665</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-3282</v>
+        <v>-747</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -788,9 +788,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4826</v>
+        <v>8707</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7687</v>
+        <v>10159</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-2861</v>
+        <v>-1452</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -833,9 +833,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,12 +847,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4826</v>
+        <v>7918</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7687</v>
+        <v>8665</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-2861</v>
+        <v>-747</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -878,9 +878,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,12 +892,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07-APR-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -906,13 +906,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6663</v>
+        <v>7918</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7687</v>
+        <v>10159</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1024</v>
+        <v>-2241</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>07-APR-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6663</v>
+        <v>7298</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7687</v>
+        <v>7946</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1024</v>
+        <v>-648</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -982,12 +982,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>17-APR-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6663</v>
+        <v>7918</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7687</v>
+        <v>10159</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1024</v>
+        <v>-2241</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>17-APR-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6663</v>
+        <v>7298</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>7687</v>
+        <v>8665</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1024</v>
+        <v>-1367</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1072,12 +1072,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1086,22 +1086,22 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9385</v>
+        <v>7298</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11335</v>
+        <v>8242</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1950</v>
+        <v>-944</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9385</v>
+        <v>7298</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>11335</v>
+        <v>7946</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1950</v>
+        <v>-648</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7898</v>
+        <v>7298</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>9609</v>
+        <v>7946</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1711</v>
+        <v>-648</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1207,12 +1207,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SM-447</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7898</v>
+        <v>7298</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>9609</v>
+        <v>7946</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-1711</v>
+        <v>-648</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1252,12 +1252,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7281</v>
+        <v>7918</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7393</v>
+        <v>7946</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-112</v>
+        <v>-28</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1297,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7393</v>
+        <v>7946</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-112</v>
+        <v>-648</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1342,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1356,13 +1356,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>9609</v>
+        <v>8242</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-2328</v>
+        <v>-944</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1387,12 +1387,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SM-447</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7281</v>
+        <v>7918</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>9609</v>
+        <v>8242</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-2328</v>
+        <v>-324</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1432,12 +1432,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1446,13 +1446,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7281</v>
+        <v>10102</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>7393</v>
+        <v>11300</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-112</v>
+        <v>-1198</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1477,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>7281</v>
+        <v>10102</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>7393</v>
+        <v>11300</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-112</v>
+        <v>-1198</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1522,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7281</v>
+        <v>10807</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>9609</v>
+        <v>11300</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-2328</v>
+        <v>-493</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1567,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7281</v>
+        <v>10807</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>9609</v>
+        <v>11906</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-2328</v>
+        <v>-1099</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>30</v>
@@ -1612,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7281</v>
+        <v>10807</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>7393</v>
+        <v>11300</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-112</v>
+        <v>-493</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>30</v>
@@ -1657,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>7281</v>
+        <v>10102</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>7393</v>
+        <v>11300</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-112</v>
+        <v>-1198</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>30</v>
@@ -1702,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1716,13 +1716,13 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>7281</v>
+        <v>10102</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>9609</v>
+        <v>11300</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-2328</v>
+        <v>-1198</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>30</v>
@@ -1747,12 +1747,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SM-447</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>7281</v>
+        <v>10102</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>9609</v>
+        <v>11300</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-2328</v>
+        <v>-1198</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>30</v>
@@ -1792,12 +1792,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>7393</v>
+        <v>7946</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-112</v>
+        <v>-648</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>30</v>
@@ -1837,7 +1837,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1851,13 +1851,13 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>7393</v>
+        <v>7946</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-112</v>
+        <v>-648</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>30</v>
@@ -1882,7 +1882,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1896,13 +1896,13 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>9609</v>
+        <v>7946</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-2328</v>
+        <v>-648</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>30</v>
@@ -1927,12 +1927,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SM-447</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1941,13 +1941,13 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>9609</v>
+        <v>7946</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-2328</v>
+        <v>-648</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>30</v>
@@ -1972,12 +1972,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1986,13 +1986,13 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>7393</v>
+        <v>7946</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-112</v>
+        <v>-648</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>30</v>
@@ -2017,7 +2017,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>29-SEP-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>7393</v>
+        <v>7946</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-112</v>
+        <v>-648</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>30</v>

--- a/excel_routes/route_CAI_YNB_threats.xlsx
+++ b/excel_routes/route_CAI_YNB_threats.xlsx
@@ -468,7 +468,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">

--- a/excel_routes/route_CAI_YNB_threats.xlsx
+++ b/excel_routes/route_CAI_YNB_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5593</v>
+        <v>4832</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>7946</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2353</v>
+        <v>-3114</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -639,10 +639,10 @@
         <v>7298</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10708</v>
+        <v>11300</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3410</v>
+        <v>-4002</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -653,7 +653,7 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -698,7 +698,7 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -743,7 +743,7 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -774,10 +774,10 @@
         <v>7918</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8665</v>
+        <v>7946</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-747</v>
+        <v>-28</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -788,7 +788,7 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -833,7 +833,7 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -878,7 +878,7 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -923,7 +923,7 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -968,7 +968,7 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1013,7 +1013,7 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1058,7 +1058,7 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1103,7 +1103,7 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1148,7 +1148,7 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1193,7 +1193,7 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1238,7 +1238,7 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1283,7 +1283,7 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1328,7 +1328,7 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1373,7 +1373,7 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1418,7 +1418,7 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1463,7 +1463,7 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1508,7 +1508,7 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1553,7 +1553,7 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1598,7 +1598,7 @@
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1643,7 +1643,7 @@
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1688,7 +1688,7 @@
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1733,7 +1733,7 @@
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1778,7 +1778,7 @@
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1823,7 +1823,7 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1868,7 +1868,7 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1913,7 +1913,7 @@
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1958,7 +1958,7 @@
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2003,7 +2003,7 @@
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2048,7 +2048,7 @@
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>

--- a/excel_routes/route_CAI_YNB_threats.xlsx
+++ b/excel_routes/route_CAI_YNB_threats.xlsx
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4832</v>
+        <v>4783</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3114</v>
+        <v>-3082</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4832</v>
+        <v>4783</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3114</v>
+        <v>-3082</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -636,13 +636,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7298</v>
+        <v>7223</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11300</v>
+        <v>8576</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4002</v>
+        <v>-1353</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -653,9 +653,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9412</v>
+        <v>9315</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10708</v>
+        <v>10598</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1296</v>
+        <v>-1283</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9412</v>
+        <v>9315</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>10159</v>
+        <v>10054</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-747</v>
+        <v>-739</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7918</v>
+        <v>7837</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>-28</v>
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8707</v>
+        <v>8618</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>10159</v>
+        <v>10054</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1452</v>
+        <v>-1436</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7918</v>
+        <v>7837</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8665</v>
+        <v>8576</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-747</v>
+        <v>-739</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -906,13 +906,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7918</v>
+        <v>7837</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10159</v>
+        <v>10054</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-2241</v>
+        <v>-2217</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7298</v>
+        <v>7223</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-648</v>
+        <v>-642</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7918</v>
+        <v>7837</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10159</v>
+        <v>10054</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-2241</v>
+        <v>-2217</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7298</v>
+        <v>7837</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>8665</v>
+        <v>8576</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1367</v>
+        <v>-739</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7298</v>
+        <v>7223</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>8242</v>
+        <v>8158</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-944</v>
+        <v>-935</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7298</v>
+        <v>7223</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-648</v>
+        <v>-642</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7298</v>
+        <v>7223</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-648</v>
+        <v>-642</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7298</v>
+        <v>7223</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-648</v>
+        <v>-642</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7918</v>
+        <v>7837</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>-28</v>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7298</v>
+        <v>7223</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-648</v>
+        <v>-642</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1356,13 +1356,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7298</v>
+        <v>7223</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>8242</v>
+        <v>8158</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-944</v>
+        <v>-935</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7918</v>
+        <v>7837</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>8242</v>
+        <v>8158</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-324</v>
+        <v>-321</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1446,13 +1446,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>10102</v>
+        <v>9998</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>11300</v>
+        <v>11184</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-1198</v>
+        <v>-1186</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10102</v>
+        <v>9998</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11300</v>
+        <v>11184</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1198</v>
+        <v>-1186</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>10807</v>
+        <v>10696</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>11300</v>
+        <v>11184</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-493</v>
+        <v>-488</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>10807</v>
+        <v>10696</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11906</v>
+        <v>11783</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-1099</v>
+        <v>-1087</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>30</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>10807</v>
+        <v>10696</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>11300</v>
+        <v>11184</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-493</v>
+        <v>-488</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>30</v>
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>10102</v>
+        <v>9998</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>11300</v>
+        <v>11184</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-1198</v>
+        <v>-1186</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>30</v>
@@ -1716,13 +1716,13 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>10102</v>
+        <v>9998</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>11300</v>
+        <v>11184</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-1198</v>
+        <v>-1186</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>30</v>
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>10102</v>
+        <v>9998</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11300</v>
+        <v>11184</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-1198</v>
+        <v>-1186</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>30</v>
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>7298</v>
+        <v>7223</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-648</v>
+        <v>-642</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>30</v>
@@ -1851,13 +1851,13 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7298</v>
+        <v>7223</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-648</v>
+        <v>-642</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>30</v>
@@ -1896,13 +1896,13 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>7298</v>
+        <v>7223</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-648</v>
+        <v>-642</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>30</v>
@@ -1941,13 +1941,13 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7298</v>
+        <v>7223</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-648</v>
+        <v>-642</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>30</v>
@@ -1986,13 +1986,13 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7298</v>
+        <v>7223</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-648</v>
+        <v>-642</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>30</v>
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>7298</v>
+        <v>7223</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>7946</v>
+        <v>7865</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-648</v>
+        <v>-642</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>30</v>

--- a/excel_routes/route_CAI_YNB_threats.xlsx
+++ b/excel_routes/route_CAI_YNB_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -459,7 +459,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4783</v>
+        <v>4855</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4936</v>
+        <v>5011</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-153</v>
+        <v>-156</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -556,7 +556,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7837</v>
+        <v>8748</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9050</v>
+        <v>9187</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-1213</v>
+        <v>-439</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -601,415 +601,10 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>27-JUN-26</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SM-447</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>7837</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>9050</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>-1213</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>01-AUG-26</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SM-447</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>9970</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>11128</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-1158</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>04-AUG-26</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>9970</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>11128</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-1158</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>08-AUG-26</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>SM-447</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>10668</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>11128</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>-460</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>15-AUG-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-447</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>10668</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>12299</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-1631</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25-AUG-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>10668</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>11128</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-460</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>01-SEP-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>9970</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>11128</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-1158</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>05-SEP-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-447</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>9970</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>11128</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-1158</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>08-SEP-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>9970</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>11128</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-1158</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_YNB_threats.xlsx
+++ b/excel_routes/route_CAI_YNB_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -565,51 +565,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>06-JUN-26</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>SM-447</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>8748</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>9187</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>-439</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel_routes/route_CAI_YNB_threats.xlsx
+++ b/excel_routes/route_CAI_YNB_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4855</v>
+        <v>4833</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5011</v>
+        <v>4988</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-156</v>
+        <v>-155</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -560,6 +560,501 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SM-447</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>8709</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>9160</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-451</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>20-JUN-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-447</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>7299</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>9160</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-1861</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>27-JUN-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-447</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>7299</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>9160</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-1861</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>01-AUG-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-447</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>10076</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>11259</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-1183</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-441</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>10076</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>11259</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-1183</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-447</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>10809</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>11259</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-450</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-447</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>11570</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>12457</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-887</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>25-AUG-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-441</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>10809</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>11259</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-450</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-441</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>10076</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>11259</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-1183</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>05-SEP-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-447</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>10809</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>11259</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-450</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-441</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-103</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>10076</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>11259</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-1183</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_YNB_threats.xlsx
+++ b/excel_routes/route_CAI_YNB_threats.xlsx
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10076</v>
+        <v>10104</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>11259</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1183</v>
+        <v>-1155</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>10076</v>
+        <v>10104</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>11259</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1183</v>
+        <v>-1155</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10076</v>
+        <v>10809</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>11259</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1183</v>
+        <v>-450</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10076</v>
+        <v>10104</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>11259</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1183</v>
+        <v>-1155</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>

--- a/excel_routes/route_CAI_YNB_threats.xlsx
+++ b/excel_routes/route_CAI_YNB_threats.xlsx
@@ -523,12 +523,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4833</v>
+        <v>6659</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4988</v>
+        <v>7720</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-155</v>
+        <v>-1061</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -568,12 +568,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-447</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8709</v>
+        <v>7888</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9160</v>
+        <v>8432</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-451</v>
+        <v>-544</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7299</v>
+        <v>7273</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9160</v>
+        <v>9130</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-1861</v>
+        <v>-1857</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7299</v>
+        <v>7273</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9160</v>
+        <v>9130</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1861</v>
+        <v>-1857</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10104</v>
+        <v>10080</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11259</v>
+        <v>11239</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1155</v>
+        <v>-1159</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>10104</v>
+        <v>10080</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11259</v>
+        <v>11239</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1155</v>
+        <v>-1159</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>10809</v>
+        <v>10778</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11259</v>
+        <v>11239</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-450</v>
+        <v>-461</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>11570</v>
+        <v>11560</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12457</v>
+        <v>12439</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-887</v>
+        <v>-879</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10809</v>
+        <v>10778</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11259</v>
+        <v>11239</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-450</v>
+        <v>-461</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10809</v>
+        <v>10778</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11259</v>
+        <v>11239</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-450</v>
+        <v>-461</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10809</v>
+        <v>10778</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11259</v>
+        <v>11239</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-450</v>
+        <v>-461</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10104</v>
+        <v>10080</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11259</v>
+        <v>11239</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1155</v>
+        <v>-1159</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>

--- a/excel_routes/route_CAI_YNB_threats.xlsx
+++ b/excel_routes/route_CAI_YNB_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6659</v>
+        <v>7189</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7720</v>
+        <v>9039</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-1061</v>
+        <v>-1850</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -568,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7888</v>
+        <v>6003</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8432</v>
+        <v>6651</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-544</v>
+        <v>-648</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -613,7 +613,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7273</v>
+        <v>7189</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9130</v>
+        <v>9039</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-1857</v>
+        <v>-1850</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -658,7 +658,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7273</v>
+        <v>9963</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9130</v>
+        <v>11123</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1857</v>
+        <v>-1160</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -703,12 +703,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-447</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10080</v>
+        <v>9963</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11239</v>
+        <v>11123</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1159</v>
+        <v>-1160</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -748,12 +748,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>10080</v>
+        <v>10681</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11239</v>
+        <v>11123</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1159</v>
+        <v>-442</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -793,7 +793,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>10778</v>
+        <v>10681</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11239</v>
+        <v>12323</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-461</v>
+        <v>-1642</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -838,7 +838,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>22-AUG-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>11560</v>
+        <v>11454</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12439</v>
+        <v>12323</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-879</v>
+        <v>-869</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -883,7 +883,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10778</v>
+        <v>10681</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11239</v>
+        <v>11123</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-461</v>
+        <v>-442</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -928,12 +928,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10778</v>
+        <v>10681</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11239</v>
+        <v>11123</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-461</v>
+        <v>-442</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -973,12 +973,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-447</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10778</v>
+        <v>9963</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11239</v>
+        <v>11123</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-461</v>
+        <v>-1160</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1010,51 +1010,6 @@
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>08-SEP-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-441</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-103</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>10080</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>11239</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-1159</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
